--- a/data/trans_orig/P36B17-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B17-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>159370</t>
+          <t>172219</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>138150</t>
+          <t>150886</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>182170</t>
+          <t>193805</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>140236</t>
+          <t>155664</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>122824</t>
+          <t>139671</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>156717</t>
+          <t>173678</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>299607</t>
+          <t>327883</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>272144</t>
+          <t>298841</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>325857</t>
+          <t>354317</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>163787</t>
+          <t>180118</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>144123</t>
+          <t>159242</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>186710</t>
+          <t>204050</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>175201</t>
+          <t>192062</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>157423</t>
+          <t>174602</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>193926</t>
+          <t>211846</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>338989</t>
+          <t>372180</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>310474</t>
+          <t>342057</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>366980</t>
+          <t>401440</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,67%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>146307</t>
+          <t>156893</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>124979</t>
+          <t>133058</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>168617</t>
+          <t>180959</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>121971</t>
+          <t>129991</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>104498</t>
+          <t>113661</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140140</t>
+          <t>149622</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>268278</t>
+          <t>286884</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>240755</t>
+          <t>259160</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>298136</t>
+          <t>315896</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28768</t>
+          <t>33583</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19948</t>
+          <t>23941</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40502</t>
+          <t>49229</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6353</t>
+          <t>6680</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12244</t>
+          <t>11930</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>35121</t>
+          <t>40262</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24844</t>
+          <t>29089</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48019</t>
+          <t>55587</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13594</t>
+          <t>14750</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>794</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>7376</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>9825</t>
+          <t>10921</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17571</t>
+          <t>19901</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>446607</t>
+          <t>487513</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>446607</t>
+          <t>487513</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>446607</t>
+          <t>487513</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>951820</t>
+          <t>1038131</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>951820</t>
+          <t>1038131</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>951820</t>
+          <t>1038131</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,27 +1407,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>118540</t>
+          <t>127745</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>100893</t>
+          <t>108959</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>139335</t>
+          <t>148945</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>110653</t>
+          <t>123920</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96222</t>
+          <t>108486</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125638</t>
+          <t>141930</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>229194</t>
+          <t>251664</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>207122</t>
+          <t>224827</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>256065</t>
+          <t>277495</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,7%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>160314</t>
+          <t>172078</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>139196</t>
+          <t>151860</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>181660</t>
+          <t>193492</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>142957</t>
+          <t>160258</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127496</t>
+          <t>143468</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159370</t>
+          <t>179026</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>303271</t>
+          <t>332335</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>277324</t>
+          <t>304623</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>329087</t>
+          <t>360464</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,88%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>144013</t>
+          <t>152132</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>122416</t>
+          <t>130441</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>166340</t>
+          <t>175193</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>102083</t>
+          <t>109434</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>86999</t>
+          <t>93925</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>118601</t>
+          <t>124405</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>246097</t>
+          <t>261565</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>222125</t>
+          <t>236085</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>273336</t>
+          <t>291047</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,2%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18531</t>
+          <t>19948</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10296</t>
+          <t>11566</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31953</t>
+          <t>34614</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>24578</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14894</t>
+          <t>16694</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31166</t>
+          <t>35161</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>40852</t>
+          <t>44525</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29642</t>
+          <t>31660</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56192</t>
+          <t>59766</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -1859,22 +1859,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8351</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15846</t>
+          <t>16807</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9855</t>
+          <t>10952</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>12915</t>
+          <t>13833</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21786</t>
+          <t>22034</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>449748</t>
+          <t>480781</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>449748</t>
+          <t>480781</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>449748</t>
+          <t>480781</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>832329</t>
+          <t>903923</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>832329</t>
+          <t>903923</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>832329</t>
+          <t>903923</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>108980</t>
+          <t>117929</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40955</t>
+          <t>98899</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>179097</t>
+          <t>138539</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>51479</t>
+          <t>58047</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42254</t>
+          <t>48504</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61047</t>
+          <t>69785</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>160460</t>
+          <t>175976</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72183</t>
+          <t>154304</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>236038</t>
+          <t>199445</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>146613</t>
+          <t>167996</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58673</t>
+          <t>149461</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>241917</t>
+          <t>190279</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>58078</t>
+          <t>66651</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49491</t>
+          <t>56024</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69439</t>
+          <t>78324</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>204690</t>
+          <t>234647</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>97729</t>
+          <t>209850</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>297428</t>
+          <t>258101</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>39,19%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>144044</t>
+          <t>158579</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58729</t>
+          <t>137399</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>239145</t>
+          <t>180591</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>48518</t>
+          <t>53588</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39479</t>
+          <t>43882</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57946</t>
+          <t>65016</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>192562</t>
+          <t>212167</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>89010</t>
+          <t>187964</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>280468</t>
+          <t>235623</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>35,78%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18018</t>
+          <t>19409</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5755</t>
+          <t>12192</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>29678</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2315</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9601</t>
+          <t>9975</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>23074</t>
+          <t>24653</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9558</t>
+          <t>16633</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37143</t>
+          <t>35994</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>250609</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6331</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>500001</t>
+          <t>14852</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>253856</t>
+          <t>11142</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10915</t>
+          <t>5854</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>564733</t>
+          <t>18503</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>166379</t>
+          <t>186973</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>166379</t>
+          <t>186973</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>166379</t>
+          <t>186973</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>834643</t>
+          <t>658584</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>834643</t>
+          <t>658584</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>834643</t>
+          <t>658584</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>255529</t>
+          <t>283164</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>228755</t>
+          <t>252943</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>286233</t>
+          <t>311632</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>391823</t>
+          <t>216135</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>230764</t>
+          <t>195130</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>660987</t>
+          <t>238058</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>647352</t>
+          <t>499299</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>482667</t>
+          <t>462342</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1044766</t>
+          <t>536188</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>312386</t>
+          <t>341635</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>283090</t>
+          <t>309480</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>346831</t>
+          <t>375857</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>281122</t>
+          <t>304623</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>154739</t>
+          <t>282109</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>363988</t>
+          <t>330526</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>593508</t>
+          <t>646259</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>416396</t>
+          <t>606406</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>676250</t>
+          <t>688350</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>357909</t>
+          <t>386368</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>322984</t>
+          <t>351841</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>392991</t>
+          <t>421294</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>244523</t>
+          <t>271139</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>125307</t>
+          <t>247717</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>317550</t>
+          <t>295011</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>602432</t>
+          <t>657507</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>430012</t>
+          <t>610207</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>683669</t>
+          <t>705039</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>35,45%</t>
         </is>
       </c>
     </row>
@@ -3110,102 +3110,102 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>82022</t>
+          <t>91273</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>64090</t>
+          <t>72377</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>104890</t>
+          <t>119086</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>6,39%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>10,52%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>53958</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>42159</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>68305</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>6,29%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>4,92%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>7,97%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>145230</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>123177</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>174622</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>6,19%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>10,14%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>48922</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>25461</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>69442</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>7,13%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>130944</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>93885</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>161869</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>6,52%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>26973</t>
+          <t>29404</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16409</t>
+          <t>19162</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>39537</t>
+          <t>43479</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>7762</t>
+          <t>11341</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>5736</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13716</t>
+          <t>20351</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>34735</t>
+          <t>40744</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21367</t>
+          <t>29156</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>50448</t>
+          <t>58721</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>974152</t>
+          <t>857196</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>974152</t>
+          <t>857196</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>974152</t>
+          <t>857196</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2008971</t>
+          <t>1989039</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2008971</t>
+          <t>1989039</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2008971</t>
+          <t>1989039</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>108743</t>
+          <t>140031</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>93258</t>
+          <t>118745</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>129421</t>
+          <t>160381</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>229870</t>
+          <t>258327</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>173848</t>
+          <t>235958</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>266080</t>
+          <t>277827</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>338613</t>
+          <t>398358</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>280672</t>
+          <t>367453</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>377128</t>
+          <t>428461</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>30,74%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>144277</t>
+          <t>176495</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>123518</t>
+          <t>151624</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>168026</t>
+          <t>200565</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>235866</t>
+          <t>265114</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>173883</t>
+          <t>243778</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>271867</t>
+          <t>286931</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>380143</t>
+          <t>441609</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>311061</t>
+          <t>409010</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>419132</t>
+          <t>475450</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>156427</t>
+          <t>178957</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>135216</t>
+          <t>155807</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>180875</t>
+          <t>203077</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>327890</t>
+          <t>252430</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>260325</t>
+          <t>232461</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>453766</t>
+          <t>275483</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>484318</t>
+          <t>431387</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>418848</t>
+          <t>397009</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>630126</t>
+          <t>462833</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>33,21%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>49422</t>
+          <t>53665</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>36923</t>
+          <t>39658</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>66777</t>
+          <t>71934</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>33437</t>
+          <t>37521</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>22601</t>
+          <t>27492</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>46392</t>
+          <t>50454</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>82859</t>
+          <t>91186</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>61942</t>
+          <t>73366</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>101650</t>
+          <t>111568</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>15013</t>
+          <t>17674</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>10561</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>25438</t>
+          <t>29402</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>12246</t>
+          <t>13626</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>7969</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>20223</t>
+          <t>21512</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>27260</t>
+          <t>31300</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>17859</t>
+          <t>22241</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>40056</t>
+          <t>44663</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>473882</t>
+          <t>566822</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>473882</t>
+          <t>566822</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>473882</t>
+          <t>566822</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>839310</t>
+          <t>827018</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>839310</t>
+          <t>827018</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>839310</t>
+          <t>827018</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1313192</t>
+          <t>1393840</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1313192</t>
+          <t>1393840</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1313192</t>
+          <t>1393840</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>50973</t>
+          <t>53107</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>33229</t>
+          <t>36639</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>74262</t>
+          <t>74828</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>232578</t>
+          <t>256696</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>211125</t>
+          <t>232921</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>255710</t>
+          <t>281319</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>283551</t>
+          <t>309804</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>253599</t>
+          <t>282053</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>313269</t>
+          <t>341247</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,59%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>65022</t>
+          <t>61147</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>43688</t>
+          <t>41906</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>88467</t>
+          <t>83732</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>276040</t>
+          <t>305338</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>252883</t>
+          <t>280180</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>302369</t>
+          <t>333970</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>341062</t>
+          <t>366486</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>310248</t>
+          <t>332968</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>376962</t>
+          <t>402413</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,25%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>92978</t>
+          <t>89090</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>68969</t>
+          <t>67884</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>121042</t>
+          <t>114508</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>200804</t>
+          <t>224227</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>176355</t>
+          <t>198046</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>226157</t>
+          <t>252065</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>293782</t>
+          <t>313317</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>258675</t>
+          <t>277519</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>331728</t>
+          <t>350023</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>20307</t>
+          <t>18600</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>48334</t>
+          <t>44162</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>39178</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>27622</t>
+          <t>32996</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>53564</t>
+          <t>61836</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>59485</t>
+          <t>64263</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>42972</t>
+          <t>46528</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>92311</t>
+          <t>91250</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>11227</t>
+          <t>15283</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>23671</t>
+          <t>31925</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>9366</t>
+          <t>11100</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>17963</t>
+          <t>21235</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>20593</t>
+          <t>26384</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>11816</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>34894</t>
+          <t>42836</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>757967</t>
+          <t>843025</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>757967</t>
+          <t>843025</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>757967</t>
+          <t>843025</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>998474</t>
+          <t>1080253</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>998474</t>
+          <t>1080253</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>998474</t>
+          <t>1080253</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>802136</t>
+          <t>894195</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>594174</t>
+          <t>842805</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>884244</t>
+          <t>951310</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1156640</t>
+          <t>1068790</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>988041</t>
+          <t>1020173</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1578956</t>
+          <t>1114213</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>1958775</t>
+          <t>1962984</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1746935</t>
+          <t>1891638</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2477015</t>
+          <t>2038262</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>992398</t>
+          <t>1099470</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>716813</t>
+          <t>1038071</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1091231</t>
+          <t>1161379</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>1169265</t>
+          <t>1294047</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>948118</t>
+          <t>1241938</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1271570</t>
+          <t>1347494</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>2161663</t>
+          <t>2393516</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1882415</t>
+          <t>2310219</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2318756</t>
+          <t>2466713</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>34,92%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1041680</t>
+          <t>1122018</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>760367</t>
+          <t>1060943</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1145794</t>
+          <t>1184351</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>1045789</t>
+          <t>1040809</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>881980</t>
+          <t>987908</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1193296</t>
+          <t>1090418</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>2087469</t>
+          <t>2162827</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1813917</t>
+          <t>2079722</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2275759</t>
+          <t>2238378</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -5156,102 +5156,102 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>217066</t>
+          <t>236478</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>166668</t>
+          <t>200084</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>261197</t>
+          <t>273209</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
+          <t>6,88%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>5,82%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>7,94%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>173643</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>151543</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>202564</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>4,79%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>4,18%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>5,59%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>410120</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>368680</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>455167</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>5,81%</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>5,22%</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
           <t>6,44%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>155269</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>126920</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>182234</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>5,11%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>372335</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>316616</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>424806</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>5,37%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>319153</t>
+          <t>86743</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>74334</t>
+          <t>68253</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1194262</t>
+          <t>115006</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>40032</t>
+          <t>47581</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>29569</t>
+          <t>35130</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>54677</t>
+          <t>62167</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>359185</t>
+          <t>134324</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>112013</t>
+          <t>111167</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1196385</t>
+          <t>161652</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3372433</t>
+          <t>3438903</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>3372433</t>
+          <t>3438903</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>3372433</t>
+          <t>3438903</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>3566995</t>
+          <t>3624869</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>3566995</t>
+          <t>3624869</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3566995</t>
+          <t>3624869</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>6939428</t>
+          <t>7063771</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>6939428</t>
+          <t>7063771</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>6939428</t>
+          <t>7063771</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
